--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_354_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_354_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4639</v>
+        <v>6.0565</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5222</v>
+        <v>5.8459</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0583</v>
+        <v>0.2105</v>
       </c>
       <c r="G2" t="n">
         <v>3.2585</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1863</v>
+        <v>-0.5937</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0736</v>
+        <v>0.3973</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2599</v>
+        <v>-0.9911</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1423</v>
+        <v>3.4919</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1042</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0381</v>
+        <v>3.3996</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0543</v>
@@ -688,13 +688,13 @@
         <v>3.9432</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1243</v>
+        <v>-0.5261</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3848</v>
+        <v>-0.3967</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5092</v>
+        <v>-0.1294</v>
       </c>
       <c r="V3" t="n">
         <v>2.6805</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.163</v>
+        <v>2.4138</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.2513</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7996</v>
+        <v>2.6651</v>
       </c>
       <c r="G4" t="n">
         <v>0.7432</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6677</v>
+        <v>-0.4169</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3576</v>
+        <v>0.0277</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3101</v>
+        <v>-0.4446</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4816</v>
+        <v>2.244</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1093</v>
+        <v>0.3506</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5909</v>
+        <v>1.8934</v>
       </c>
       <c r="G5" t="n">
         <v>0.592</v>
@@ -844,13 +844,13 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6619</v>
+        <v>-0.8995</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7978</v>
+        <v>-0.3378</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8641</v>
+        <v>-0.5616</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9796</v>
+        <v>1.7853</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1474</v>
+        <v>-0.6442</v>
       </c>
       <c r="F6" t="n">
-        <v>2.127</v>
+        <v>2.4295</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4824</v>
@@ -922,13 +922,13 @@
         <v>3.4793</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.2005</v>
+        <v>-1.3948</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7231</v>
+        <v>-0.2199</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.4774</v>
+        <v>-1.1749</v>
       </c>
       <c r="V6" t="n">
         <v>3.8945</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5827</v>
+        <v>0.6238</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2441</v>
+        <v>1.3188</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6614</v>
+        <v>-0.695</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0699</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5768</v>
+        <v>-0.5357</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7468</v>
+        <v>-0.6721</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.1364</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3943</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2701</v>
+        <v>0.3619</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3075</v>
+        <v>0.5001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0374</v>
+        <v>-0.1382</v>
       </c>
       <c r="G8" t="n">
         <v>0.5183</v>
@@ -1078,13 +1078,13 @@
         <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.176</v>
+        <v>-1.0842</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8883</v>
+        <v>-0.6956</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2877</v>
+        <v>-0.3886</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.775</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>-0.6824</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0925</v>
+        <v>-0.0589</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0964</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0523</v>
+        <v>-0.0187</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V9" t="n">
         <v>0.1418</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.187</v>
+        <v>-1.9944</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1432</v>
+        <v>0.3359</v>
       </c>
       <c r="F10" t="n">
         <v>-2.3303</v>
@@ -1234,10 +1234,10 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.093</v>
+        <v>-0.9003</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9709</v>
+        <v>-0.7782</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1221</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.1212</v>
+        <v>14.2414</v>
       </c>
       <c r="E11" t="n">
-        <v>5.7455</v>
+        <v>6.8657</v>
       </c>
       <c r="F11" t="n">
         <v>7.3757</v>
@@ -1312,13 +1312,13 @@
         <v>20.8759</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.4902</v>
+        <v>-6.369899999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.8704</v>
+        <v>-2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.6197</v>
+        <v>-3.6199</v>
       </c>
       <c r="V11" t="n">
         <v>6.3225</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.8862</v>
+        <v>5.5613</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0268</v>
+        <v>4.6916</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8593</v>
+        <v>0.8697</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1484</v>
+        <v>4.1903</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0841</v>
+        <v>0.0682</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0643</v>
+        <v>4.1222</v>
       </c>
       <c r="J12" t="n">
-        <v>2.784</v>
+        <v>5.4993</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8234</v>
+        <v>1.0593</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9606</v>
+        <v>4.44</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3644</v>
+        <v>-1.309</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2606</v>
+        <v>-0.9912</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1038</v>
+        <v>-0.3178</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4639</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.3917</v>
+        <v>-3.4793</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1294</v>
+        <v>1.3142</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5623</v>
+        <v>0.5272</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5671</v>
+        <v>0.787</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7185</v>
+        <v>4.4987</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2198</v>
+        <v>2.673</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4987</v>
+        <v>1.8257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1903</v>
+        <v>3.1484</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0682</v>
+        <v>1.0841</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1222</v>
+        <v>2.0643</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4993</v>
+        <v>2.784</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0593</v>
+        <v>0.8234</v>
       </c>
       <c r="L13" t="n">
-        <v>4.44</v>
+        <v>1.9606</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.309</v>
+        <v>0.3644</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9912</v>
+        <v>0.2606</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3178</v>
+        <v>0.1038</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4714</v>
+        <v>0.742</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0553</v>
+        <v>0.2084</v>
       </c>
       <c r="U13" t="n">
-        <v>0.416</v>
+        <v>0.5335</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.7695</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1155</v>
+        <v>-0.1974</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4618</v>
+        <v>0.9668</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2109</v>
+        <v>0.1605</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0634</v>
+        <v>-0.4585</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2743</v>
+        <v>0.619</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9083</v>
+        <v>-0.0678</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3697</v>
+        <v>-0.215</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5386</v>
+        <v>0.1472</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6974</v>
+        <v>0.2283</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4331</v>
+        <v>-0.2435</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2643</v>
+        <v>0.4718</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R14" t="n">
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1233</v>
+        <v>0.4492</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2072</v>
+        <v>0.1024</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0839</v>
+        <v>0.3468</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5316</v>
+        <v>0.5301</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.782</v>
+        <v>1.6437</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3136</v>
+        <v>-1.1137</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.7455</v>
+        <v>0.2109</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2159</v>
+        <v>-0.0634</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.5296</v>
+        <v>0.2743</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.3092</v>
+        <v>0.9083</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0973</v>
+        <v>0.3697</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.2118</v>
+        <v>0.5386</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4364</v>
+        <v>-0.6974</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1186</v>
+        <v>-0.4331</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3178</v>
+        <v>-0.2643</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1174</v>
+        <v>0.9996</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7591</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3583</v>
+        <v>0.2642</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3427</v>
+        <v>0.0497</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4333</v>
+        <v>-2.0179</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7759</v>
+        <v>2.0676</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1605</v>
+        <v>-2.7455</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4585</v>
+        <v>-0.2159</v>
       </c>
       <c r="I16" t="n">
-        <v>0.619</v>
+        <v>-2.5296</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0678</v>
+        <v>-2.3092</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.215</v>
+        <v>-0.0973</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1472</v>
+        <v>-2.2118</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2283</v>
+        <v>-0.4364</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2435</v>
+        <v>-0.1186</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4718</v>
+        <v>-0.3178</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0224</v>
+        <v>1.6355</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1336</v>
+        <v>0.5232</v>
       </c>
       <c r="U16" t="n">
-        <v>0.156</v>
+        <v>1.1123</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1606</v>
+        <v>-0.1384</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2077</v>
+        <v>-0.4436</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0472</v>
+        <v>0.3052</v>
       </c>
       <c r="G17" t="n">
         <v>0.2719</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5623</v>
+        <v>0.3264</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0154</v>
+        <v>0.2427</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2836</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9498</v>
+        <v>-1.1977</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0847</v>
+        <v>-0.8488</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8651</v>
+        <v>-0.3489</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9744</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2074</v>
+        <v>0.5447</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2355</v>
+        <v>0.0004</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0281</v>
+        <v>0.5443</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0456</v>
+        <v>-1.7032</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4012</v>
+        <v>-2.2833</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3556</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.8374</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7407</v>
+        <v>1.0831</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5623</v>
+        <v>0.6803</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1784</v>
+        <v>0.4028</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3218</v>
+        <v>-2.0523</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8807</v>
+        <v>1.1166</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2025</v>
+        <v>-3.1689</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2799</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2016</v>
+        <v>0.0679</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3658</v>
+        <v>-3.5972</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2029</v>
+        <v>-1.085</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1629</v>
+        <v>-2.5123</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3282</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5737</v>
+        <v>0.1948</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3181</v>
+        <v>-0.2001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2557</v>
+        <v>0.3949</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.935</v>
+        <v>-5.013</v>
       </c>
       <c r="E22" t="n">
         <v>-2.8192</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1158</v>
+        <v>-2.1938</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1595</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6884</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="T22" t="n">
         <v>0.1221</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5663</v>
+        <v>0.4883</v>
       </c>
       <c r="V22" t="n">
         <v>-2.6805</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.4754</v>
+        <v>-8.4697</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.6875</v>
+        <v>-7.8055</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.6642</v>
       </c>
       <c r="G23" t="n">
         <v>-6.3428</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>1.6329</v>
+        <v>1.6386</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7749</v>
+        <v>0.657</v>
       </c>
       <c r="U23" t="n">
-        <v>0.858</v>
+        <v>0.9816</v>
       </c>
       <c r="V23" t="n">
         <v>-1.214</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.1213</v>
+        <v>-10.7622</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.375699999999999</v>
+        <v>-7.3758</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.7456</v>
+        <v>-3.3867</v>
       </c>
       <c r="G24" t="n">
         <v>-5.0109</v>
@@ -2299,7 +2299,7 @@
         <v>5.018400000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>4.913200000000001</v>
+        <v>4.913200000000002</v>
       </c>
       <c r="K24" t="n">
         <v>-1.4427</v>
@@ -2326,13 +2326,13 @@
         <v>11.5977</v>
       </c>
       <c r="S24" t="n">
-        <v>7.4901</v>
+        <v>9.8491</v>
       </c>
       <c r="T24" t="n">
-        <v>3.6196</v>
+        <v>3.6199</v>
       </c>
       <c r="U24" t="n">
-        <v>3.870300000000001</v>
+        <v>6.2291</v>
       </c>
       <c r="V24" t="n">
         <v>-6.3225</v>
